--- a/TestCase of Google Classroom Application.xlsx
+++ b/TestCase of Google Classroom Application.xlsx
@@ -17,9 +17,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>TC_Practical-001</t>
   </si>
   <si>
     <t>Test Case Desc</t>
@@ -348,6 +345,9 @@
       </rPr>
       <t xml:space="preserve"> Sign out.</t>
     </r>
+  </si>
+  <si>
+    <t>TC_Practical-008</t>
   </si>
 </sst>
 </file>
@@ -754,10 +754,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -767,15 +763,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -785,17 +772,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -812,17 +790,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -832,18 +805,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -851,20 +818,53 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -881,6 +881,48 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123826</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>438150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1104901</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1695449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="3685" t="3955" r="2225" b="2273"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1000126" y="4733925"/>
+          <a:ext cx="1714500" cy="1257299"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1102,24 +1144,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>2</v>
+      <c r="E1" s="7"/>
+      <c r="F1" s="41" t="s">
+        <v>20</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="12"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -1137,27 +1179,27 @@
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="G2" s="30"/>
+      <c r="H2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="20" t="s">
-        <v>18</v>
+      <c r="I2" s="30"/>
+      <c r="J2" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1176,22 +1218,22 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="22"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="12"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1209,16 +1251,16 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="25"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="15"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1236,23 +1278,23 @@
       <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
       <c r="J5" s="31"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1271,21 +1313,21 @@
       <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="32">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>22</v>
+      <c r="B6" s="28" t="s">
+        <v>21</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="33">
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="20">
         <v>1</v>
       </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="31"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1304,19 +1346,19 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="32">
+      <c r="A7" s="19">
         <v>2</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="33">
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="20">
         <v>2</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
       <c r="J7" s="31"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1335,19 +1377,19 @@
       <c r="Y7" s="1"/>
     </row>
     <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="32">
+      <c r="A8" s="19">
         <v>3</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="33">
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="20">
         <v>3</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
       <c r="J8" s="31"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1366,20 +1408,20 @@
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="34">
+      <c r="A9" s="21">
         <v>4</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="39">
+      <c r="B9" s="32"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23">
         <v>4</v>
       </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="40"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="35"/>
       <c r="K9" s="2"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1397,16 +1439,16 @@
       <c r="Y9" s="1"/>
     </row>
     <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1424,20 +1466,20 @@
       <c r="Y10" s="1"/>
     </row>
     <row r="11" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
-        <v>12</v>
+      <c r="A11" s="25" t="s">
+        <v>11</v>
       </c>
-      <c r="B11" s="43" t="s">
-        <v>54</v>
+      <c r="B11" s="46" t="s">
+        <v>53</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1455,16 +1497,16 @@
       <c r="Y11" s="1"/>
     </row>
     <row r="12" spans="1:25" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1482,16 +1524,16 @@
       <c r="Y12" s="1"/>
     </row>
     <row r="13" spans="1:25" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1509,26 +1551,26 @@
       <c r="Y13" s="1"/>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="C14" s="37"/>
+      <c r="D14" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="48" t="s">
+      <c r="E14" s="37"/>
+      <c r="F14" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="48" t="s">
+      <c r="G14" s="38"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="12"/>
+      <c r="J14" s="39"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1545,22 +1587,22 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="32">
+    <row r="15" spans="1:25" ht="143.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="18"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="28"/>
       <c r="J15" s="31"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1579,21 +1621,21 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="32">
+      <c r="A16" s="19">
         <v>2</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>55</v>
+      <c r="B16" s="28" t="s">
+        <v>54</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="18" t="s">
-        <v>25</v>
+      <c r="C16" s="30"/>
+      <c r="D16" s="28" t="s">
+        <v>24</v>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="18"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="28"/>
       <c r="J16" s="31"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1612,21 +1654,21 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" spans="1:25" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="32">
+      <c r="A17" s="19">
         <v>3</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="18"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="28"/>
       <c r="J17" s="31"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1645,21 +1687,21 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="32">
+      <c r="A18" s="19">
         <v>4</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>56</v>
+      <c r="B18" s="28" t="s">
+        <v>55</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="18" t="s">
-        <v>28</v>
+      <c r="C18" s="30"/>
+      <c r="D18" s="28" t="s">
+        <v>27</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="18"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="28"/>
       <c r="J18" s="31"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1678,21 +1720,21 @@
       <c r="Y18" s="1"/>
     </row>
     <row r="19" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="32">
+      <c r="A19" s="19">
         <v>5</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="18"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="28"/>
       <c r="J19" s="31"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1711,21 +1753,21 @@
       <c r="Y19" s="1"/>
     </row>
     <row r="20" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="32">
+      <c r="A20" s="19">
         <v>6</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>57</v>
+      <c r="B20" s="28" t="s">
+        <v>56</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="18" t="s">
-        <v>31</v>
+      <c r="C20" s="30"/>
+      <c r="D20" s="28" t="s">
+        <v>30</v>
       </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="18"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="28"/>
       <c r="J20" s="31"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1744,21 +1786,21 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="32">
+      <c r="A21" s="19">
         <v>7</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>32</v>
+      <c r="B21" s="28" t="s">
+        <v>31</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="18" t="s">
-        <v>27</v>
+      <c r="C21" s="30"/>
+      <c r="D21" s="28" t="s">
+        <v>26</v>
       </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="18"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="28"/>
       <c r="J21" s="31"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1777,21 +1819,21 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="32">
+      <c r="A22" s="19">
         <v>8</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="18"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="28"/>
       <c r="J22" s="31"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1810,21 +1852,21 @@
       <c r="Y22" s="1"/>
     </row>
     <row r="23" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="32">
+      <c r="A23" s="19">
         <v>9</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>58</v>
+      <c r="B23" s="28" t="s">
+        <v>57</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="18" t="s">
-        <v>35</v>
+      <c r="C23" s="30"/>
+      <c r="D23" s="28" t="s">
+        <v>34</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="18"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="28"/>
       <c r="J23" s="31"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1843,21 +1885,21 @@
       <c r="Y23" s="1"/>
     </row>
     <row r="24" spans="1:25" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="32">
+      <c r="A24" s="19">
         <v>10</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>59</v>
+      <c r="B24" s="28" t="s">
+        <v>58</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="18" t="s">
-        <v>36</v>
+      <c r="C24" s="30"/>
+      <c r="D24" s="28" t="s">
+        <v>35</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="18"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="28"/>
       <c r="J24" s="31"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1876,21 +1918,21 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25" spans="1:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="32">
+      <c r="A25" s="19">
         <v>11</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="18"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="28"/>
       <c r="J25" s="31"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1909,21 +1951,21 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="32">
+      <c r="A26" s="19">
         <v>12</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>60</v>
+      <c r="B26" s="28" t="s">
+        <v>59</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="18" t="s">
-        <v>39</v>
+      <c r="C26" s="30"/>
+      <c r="D26" s="28" t="s">
+        <v>38</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="18"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="28"/>
       <c r="J26" s="31"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1942,21 +1984,21 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="32">
+      <c r="A27" s="19">
         <v>13</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>61</v>
+      <c r="B27" s="28" t="s">
+        <v>60</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="18" t="s">
-        <v>40</v>
+      <c r="C27" s="30"/>
+      <c r="D27" s="28" t="s">
+        <v>39</v>
       </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="18"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="28"/>
       <c r="J27" s="31"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1975,21 +2017,21 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="32">
+      <c r="A28" s="19">
         <v>14</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="18"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="28"/>
       <c r="J28" s="31"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -2008,21 +2050,21 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="29" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="32">
+      <c r="A29" s="19">
         <v>15</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="18"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="28"/>
       <c r="J29" s="31"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -2041,21 +2083,21 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="32">
+      <c r="A30" s="19">
         <v>16</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>62</v>
+      <c r="B30" s="28" t="s">
+        <v>61</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="18" t="s">
-        <v>45</v>
+      <c r="C30" s="30"/>
+      <c r="D30" s="28" t="s">
+        <v>44</v>
       </c>
-      <c r="E30" s="14"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="18"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="28"/>
       <c r="J30" s="31"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -2074,21 +2116,21 @@
       <c r="Y30" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="32">
+      <c r="A31" s="19">
         <v>17</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>63</v>
+      <c r="B31" s="28" t="s">
+        <v>62</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="18" t="s">
-        <v>46</v>
+      <c r="C31" s="30"/>
+      <c r="D31" s="28" t="s">
+        <v>45</v>
       </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="18"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="28"/>
       <c r="J31" s="31"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -2107,21 +2149,21 @@
       <c r="Y31" s="1"/>
     </row>
     <row r="32" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="32">
+      <c r="A32" s="19">
         <v>18</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="14"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="18"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="28"/>
       <c r="J32" s="31"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2140,21 +2182,21 @@
       <c r="Y32" s="1"/>
     </row>
     <row r="33" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="32">
+      <c r="A33" s="19">
         <v>19</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="18"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="28"/>
       <c r="J33" s="31"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2173,22 +2215,22 @@
       <c r="Y33" s="1"/>
     </row>
     <row r="34" spans="1:25" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="34">
+      <c r="A34" s="21">
         <v>20</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="40"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="35"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2206,22 +2248,22 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" spans="1:25" s="3" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="34">
+      <c r="A35" s="21">
         <v>21</v>
       </c>
-      <c r="B35" s="35" t="s">
-        <v>64</v>
+      <c r="B35" s="32" t="s">
+        <v>63</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="35" t="s">
-        <v>53</v>
+      <c r="C35" s="33"/>
+      <c r="D35" s="32" t="s">
+        <v>52</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="40"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="35"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -28244,5 +28286,6 @@
   </mergeCells>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>